--- a/product_selector_out/STM32WBA5x.xlsx
+++ b/product_selector_out/STM32WBA5x.xlsx
@@ -61,12 +61,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
@@ -1350,7 +1350,7 @@
       </c>
       <c r="BP12" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba52ce.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -1692,7 +1692,7 @@
       </c>
       <c r="BP13" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba52ce.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="BP15" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba52ce.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="BP16" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba52ce.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3060,7 +3060,7 @@
       </c>
       <c r="BP17" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba52ce.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3402,7 +3402,7 @@
       </c>
       <c r="BP18" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba52ce.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
       </c>
       <c r="BP19" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba52ce.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -4428,7 +4428,7 @@
       </c>
       <c r="BP21" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba52ce.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -4770,7 +4770,7 @@
       </c>
       <c r="BP22" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba52ce.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="BP23" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba52ce.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -5454,7 +5454,7 @@
       </c>
       <c r="BP24" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba52ce.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -5796,7 +5796,7 @@
       </c>
       <c r="BP25" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba52ce.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -6436,9 +6436,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
@@ -6451,17 +6451,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J12" s="8" t="inlineStr">
+      <c r="H12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6476,7 +6476,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M12" s="8" t="inlineStr">
+      <c r="M12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6486,17 +6486,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q12" s="8" t="inlineStr">
+      <c r="O12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6526,32 +6526,32 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AA12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AB12" s="8" t="inlineStr">
+      <c r="W12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AB12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6561,22 +6561,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG12" s="8" t="inlineStr">
+      <c r="AD12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6586,7 +6586,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI12" s="8" t="inlineStr">
+      <c r="AI12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6596,7 +6596,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK12" s="8" t="inlineStr">
+      <c r="AK12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6611,12 +6611,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AO12" s="8" t="inlineStr">
+      <c r="AN12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AO12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6636,7 +6636,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS12" s="8" t="inlineStr">
+      <c r="AS12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6646,37 +6646,37 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AX12" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY12" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AZ12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BA12" s="8" t="inlineStr">
+      <c r="AU12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AX12" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY12" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AZ12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BA12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6691,37 +6691,37 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BD12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ12" s="8" t="inlineStr">
+      <c r="BD12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6731,12 +6731,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM12" s="8" t="inlineStr">
+      <c r="BL12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6751,9 +6751,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -6778,9 +6778,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
@@ -6793,17 +6793,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J13" s="8" t="inlineStr">
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6818,7 +6818,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M13" s="8" t="inlineStr">
+      <c r="M13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6828,12 +6828,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P13" s="8" t="inlineStr">
+      <c r="O13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6868,27 +6868,27 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AA13" s="8" t="inlineStr">
+      <c r="W13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6903,22 +6903,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG13" s="8" t="inlineStr">
+      <c r="AD13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6928,7 +6928,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI13" s="8" t="inlineStr">
+      <c r="AI13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6953,7 +6953,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN13" s="8" t="inlineStr">
+      <c r="AN13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6978,7 +6978,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS13" s="8" t="inlineStr">
+      <c r="AS13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6988,12 +6988,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV13" s="8" t="inlineStr">
+      <c r="AU13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7003,22 +7003,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX13" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY13" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AZ13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BA13" s="8" t="inlineStr">
+      <c r="AX13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AZ13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BA13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7043,7 +7043,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BF13" s="8" t="inlineStr">
+      <c r="BF13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7053,17 +7053,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BH13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ13" s="8" t="inlineStr">
+      <c r="BH13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7073,12 +7073,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM13" s="8" t="inlineStr">
+      <c r="BL13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7093,9 +7093,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -7120,7 +7120,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
+      <c r="E14" s="8" t="inlineStr">
         <is>
           <t>DATASHEET</t>
         </is>
@@ -7135,17 +7135,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J14" s="8" t="inlineStr">
+      <c r="H14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7160,7 +7160,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M14" s="8" t="inlineStr">
+      <c r="M14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7170,12 +7170,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P14" s="8" t="inlineStr">
+      <c r="O14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7210,27 +7210,27 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AA14" s="8" t="inlineStr">
+      <c r="W14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7245,22 +7245,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG14" s="8" t="inlineStr">
+      <c r="AD14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7270,7 +7270,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI14" s="8" t="inlineStr">
+      <c r="AI14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7295,7 +7295,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN14" s="8" t="inlineStr">
+      <c r="AN14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7320,7 +7320,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS14" s="8" t="inlineStr">
+      <c r="AS14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7330,17 +7330,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW14" s="8" t="inlineStr">
+      <c r="AU14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7350,17 +7350,17 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AY14" s="7" t="inlineStr">
+      <c r="AY14" s="8" t="inlineStr">
         <is>
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AZ14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BA14" s="8" t="inlineStr">
+      <c r="AZ14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BA14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7385,7 +7385,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BF14" s="8" t="inlineStr">
+      <c r="BF14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7395,17 +7395,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BH14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ14" s="8" t="inlineStr">
+      <c r="BH14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7415,12 +7415,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM14" s="8" t="inlineStr">
+      <c r="BL14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7462,9 +7462,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E15" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
@@ -7477,17 +7477,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J15" s="8" t="inlineStr">
+      <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7502,7 +7502,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M15" s="8" t="inlineStr">
+      <c r="M15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7512,12 +7512,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P15" s="8" t="inlineStr">
+      <c r="O15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7552,32 +7552,32 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AA15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AB15" s="8" t="inlineStr">
+      <c r="W15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AB15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7587,22 +7587,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG15" s="8" t="inlineStr">
+      <c r="AD15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7612,7 +7612,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI15" s="8" t="inlineStr">
+      <c r="AI15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7622,7 +7622,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK15" s="8" t="inlineStr">
+      <c r="AK15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7637,12 +7637,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AO15" s="8" t="inlineStr">
+      <c r="AN15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AO15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7662,7 +7662,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS15" s="8" t="inlineStr">
+      <c r="AS15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7672,37 +7672,37 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AX15" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY15" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AZ15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BA15" s="8" t="inlineStr">
+      <c r="AU15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AX15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AZ15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BA15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7717,37 +7717,37 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BD15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ15" s="8" t="inlineStr">
+      <c r="BD15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7757,12 +7757,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM15" s="8" t="inlineStr">
+      <c r="BL15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7777,9 +7777,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -7804,9 +7804,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
@@ -7819,17 +7819,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J16" s="8" t="inlineStr">
+      <c r="H16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7844,7 +7844,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M16" s="8" t="inlineStr">
+      <c r="M16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7854,12 +7854,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P16" s="8" t="inlineStr">
+      <c r="O16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7894,27 +7894,27 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AA16" s="8" t="inlineStr">
+      <c r="W16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7929,22 +7929,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG16" s="8" t="inlineStr">
+      <c r="AD16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7954,7 +7954,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI16" s="8" t="inlineStr">
+      <c r="AI16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7979,7 +7979,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN16" s="8" t="inlineStr">
+      <c r="AN16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8004,7 +8004,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS16" s="8" t="inlineStr">
+      <c r="AS16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8014,37 +8014,37 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AX16" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY16" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AZ16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BA16" s="8" t="inlineStr">
+      <c r="AU16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AX16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AZ16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BA16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8069,7 +8069,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BF16" s="8" t="inlineStr">
+      <c r="BF16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8079,17 +8079,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BH16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ16" s="8" t="inlineStr">
+      <c r="BH16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8099,12 +8099,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM16" s="8" t="inlineStr">
+      <c r="BL16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8119,9 +8119,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -8146,9 +8146,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E17" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
@@ -8161,17 +8161,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J17" s="8" t="inlineStr">
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8186,7 +8186,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M17" s="8" t="inlineStr">
+      <c r="M17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8196,17 +8196,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q17" s="8" t="inlineStr">
+      <c r="O17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8236,32 +8236,32 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AA17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AB17" s="8" t="inlineStr">
+      <c r="W17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AB17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8271,22 +8271,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG17" s="8" t="inlineStr">
+      <c r="AD17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8296,7 +8296,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI17" s="8" t="inlineStr">
+      <c r="AI17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8306,7 +8306,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK17" s="8" t="inlineStr">
+      <c r="AK17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8321,17 +8321,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AO17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AP17" s="8" t="inlineStr">
+      <c r="AN17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AO17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AP17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8346,7 +8346,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS17" s="8" t="inlineStr">
+      <c r="AS17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8356,37 +8356,37 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AX17" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY17" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AZ17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BA17" s="8" t="inlineStr">
+      <c r="AU17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AX17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AZ17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BA17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8401,37 +8401,37 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BD17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ17" s="8" t="inlineStr">
+      <c r="BD17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8441,12 +8441,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM17" s="8" t="inlineStr">
+      <c r="BL17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8461,9 +8461,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -8488,9 +8488,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E18" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr">
@@ -8503,17 +8503,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J18" s="8" t="inlineStr">
+      <c r="H18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8528,7 +8528,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M18" s="8" t="inlineStr">
+      <c r="M18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8538,12 +8538,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P18" s="8" t="inlineStr">
+      <c r="O18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8578,27 +8578,27 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AA18" s="8" t="inlineStr">
+      <c r="W18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8613,22 +8613,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG18" s="8" t="inlineStr">
+      <c r="AD18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8638,7 +8638,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI18" s="8" t="inlineStr">
+      <c r="AI18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8663,7 +8663,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN18" s="8" t="inlineStr">
+      <c r="AN18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8688,7 +8688,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS18" s="8" t="inlineStr">
+      <c r="AS18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8698,12 +8698,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV18" s="8" t="inlineStr">
+      <c r="AU18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8713,22 +8713,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX18" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY18" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AZ18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BA18" s="8" t="inlineStr">
+      <c r="AX18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AZ18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BA18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8753,7 +8753,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BF18" s="8" t="inlineStr">
+      <c r="BF18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8763,17 +8763,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BH18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ18" s="8" t="inlineStr">
+      <c r="BH18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8783,12 +8783,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM18" s="8" t="inlineStr">
+      <c r="BL18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8803,9 +8803,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -8830,9 +8830,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E19" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
@@ -8845,17 +8845,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J19" s="8" t="inlineStr">
+      <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8870,7 +8870,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M19" s="8" t="inlineStr">
+      <c r="M19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8880,12 +8880,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P19" s="8" t="inlineStr">
+      <c r="O19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8920,27 +8920,27 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AA19" s="8" t="inlineStr">
+      <c r="W19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8955,22 +8955,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG19" s="8" t="inlineStr">
+      <c r="AD19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8980,7 +8980,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI19" s="8" t="inlineStr">
+      <c r="AI19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9005,7 +9005,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN19" s="8" t="inlineStr">
+      <c r="AN19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9030,7 +9030,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS19" s="8" t="inlineStr">
+      <c r="AS19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9040,12 +9040,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV19" s="8" t="inlineStr">
+      <c r="AU19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9055,22 +9055,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX19" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY19" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AZ19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BA19" s="8" t="inlineStr">
+      <c r="AX19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AZ19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BA19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9095,7 +9095,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BF19" s="8" t="inlineStr">
+      <c r="BF19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9105,17 +9105,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BH19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ19" s="8" t="inlineStr">
+      <c r="BH19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9125,12 +9125,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM19" s="8" t="inlineStr">
+      <c r="BL19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9145,9 +9145,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -9172,7 +9172,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E20" s="7" t="inlineStr">
+      <c r="E20" s="8" t="inlineStr">
         <is>
           <t>DATASHEET</t>
         </is>
@@ -9187,17 +9187,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J20" s="8" t="inlineStr">
+      <c r="H20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J20" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9212,7 +9212,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M20" s="8" t="inlineStr">
+      <c r="M20" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9222,17 +9222,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q20" s="8" t="inlineStr">
+      <c r="O20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q20" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9262,32 +9262,32 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AA20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AB20" s="8" t="inlineStr">
+      <c r="W20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AB20" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9297,22 +9297,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG20" s="8" t="inlineStr">
+      <c r="AD20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG20" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9322,7 +9322,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI20" s="8" t="inlineStr">
+      <c r="AI20" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9332,7 +9332,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK20" s="8" t="inlineStr">
+      <c r="AK20" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9347,17 +9347,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AO20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AP20" s="8" t="inlineStr">
+      <c r="AN20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AO20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AP20" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9372,7 +9372,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS20" s="8" t="inlineStr">
+      <c r="AS20" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9382,17 +9382,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW20" s="8" t="inlineStr">
+      <c r="AU20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW20" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9402,17 +9402,17 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AY20" s="7" t="inlineStr">
+      <c r="AY20" s="8" t="inlineStr">
         <is>
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AZ20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BA20" s="8" t="inlineStr">
+      <c r="AZ20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BA20" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9427,37 +9427,37 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BD20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ20" s="8" t="inlineStr">
+      <c r="BD20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ20" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9467,12 +9467,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM20" s="8" t="inlineStr">
+      <c r="BL20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM20" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9514,9 +9514,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E21" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
@@ -9529,17 +9529,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J21" s="8" t="inlineStr">
+      <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J21" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9554,7 +9554,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M21" s="8" t="inlineStr">
+      <c r="M21" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9564,12 +9564,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P21" s="8" t="inlineStr">
+      <c r="O21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P21" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9604,27 +9604,27 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AA21" s="8" t="inlineStr">
+      <c r="W21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA21" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9639,22 +9639,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG21" s="8" t="inlineStr">
+      <c r="AD21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG21" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9664,7 +9664,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI21" s="8" t="inlineStr">
+      <c r="AI21" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9689,7 +9689,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN21" s="8" t="inlineStr">
+      <c r="AN21" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9714,7 +9714,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS21" s="8" t="inlineStr">
+      <c r="AS21" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9724,37 +9724,37 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AX21" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY21" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AZ21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BA21" s="8" t="inlineStr">
+      <c r="AU21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AX21" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY21" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AZ21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BA21" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9779,7 +9779,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BF21" s="8" t="inlineStr">
+      <c r="BF21" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9789,17 +9789,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BH21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ21" s="8" t="inlineStr">
+      <c r="BH21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ21" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9809,12 +9809,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM21" s="8" t="inlineStr">
+      <c r="BL21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM21" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9829,9 +9829,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP21" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -9856,9 +9856,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E22" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
@@ -9871,17 +9871,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J22" s="8" t="inlineStr">
+      <c r="H22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J22" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9896,7 +9896,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M22" s="8" t="inlineStr">
+      <c r="M22" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9906,12 +9906,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P22" s="8" t="inlineStr">
+      <c r="O22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P22" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9946,27 +9946,27 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AA22" s="8" t="inlineStr">
+      <c r="W22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA22" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9981,22 +9981,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG22" s="8" t="inlineStr">
+      <c r="AD22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG22" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10006,7 +10006,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI22" s="8" t="inlineStr">
+      <c r="AI22" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10031,7 +10031,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN22" s="8" t="inlineStr">
+      <c r="AN22" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10056,7 +10056,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS22" s="8" t="inlineStr">
+      <c r="AS22" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10066,37 +10066,37 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AX22" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY22" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AZ22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BA22" s="8" t="inlineStr">
+      <c r="AU22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AX22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AZ22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BA22" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10121,7 +10121,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BF22" s="8" t="inlineStr">
+      <c r="BF22" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10131,17 +10131,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BH22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ22" s="8" t="inlineStr">
+      <c r="BH22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ22" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10151,12 +10151,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM22" s="8" t="inlineStr">
+      <c r="BL22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM22" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10171,9 +10171,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -10198,9 +10198,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E23" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
@@ -10213,17 +10213,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J23" s="8" t="inlineStr">
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J23" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10238,7 +10238,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M23" s="8" t="inlineStr">
+      <c r="M23" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10248,12 +10248,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P23" s="8" t="inlineStr">
+      <c r="O23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P23" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10288,27 +10288,27 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AA23" s="8" t="inlineStr">
+      <c r="W23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA23" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10323,22 +10323,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG23" s="8" t="inlineStr">
+      <c r="AD23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG23" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10348,7 +10348,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI23" s="8" t="inlineStr">
+      <c r="AI23" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10373,7 +10373,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN23" s="8" t="inlineStr">
+      <c r="AN23" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10398,7 +10398,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS23" s="8" t="inlineStr">
+      <c r="AS23" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10408,12 +10408,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV23" s="8" t="inlineStr">
+      <c r="AU23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV23" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10423,22 +10423,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX23" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY23" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AZ23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BA23" s="8" t="inlineStr">
+      <c r="AX23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AZ23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BA23" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10463,7 +10463,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BF23" s="8" t="inlineStr">
+      <c r="BF23" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10473,17 +10473,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BH23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ23" s="8" t="inlineStr">
+      <c r="BH23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ23" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10493,12 +10493,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM23" s="8" t="inlineStr">
+      <c r="BL23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM23" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10513,9 +10513,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -10540,9 +10540,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E24" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F24" s="6" t="inlineStr">
@@ -10555,17 +10555,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J24" s="8" t="inlineStr">
+      <c r="H24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J24" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10580,7 +10580,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M24" s="8" t="inlineStr">
+      <c r="M24" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10590,12 +10590,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P24" s="8" t="inlineStr">
+      <c r="O24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P24" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10630,27 +10630,27 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AA24" s="8" t="inlineStr">
+      <c r="W24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA24" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10665,22 +10665,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG24" s="8" t="inlineStr">
+      <c r="AD24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG24" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10690,7 +10690,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI24" s="8" t="inlineStr">
+      <c r="AI24" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10715,7 +10715,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN24" s="8" t="inlineStr">
+      <c r="AN24" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10740,7 +10740,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS24" s="8" t="inlineStr">
+      <c r="AS24" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10750,37 +10750,37 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AX24" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY24" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AZ24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BA24" s="8" t="inlineStr">
+      <c r="AU24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AX24" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY24" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AZ24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BA24" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10805,7 +10805,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BF24" s="8" t="inlineStr">
+      <c r="BF24" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10815,17 +10815,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BH24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ24" s="8" t="inlineStr">
+      <c r="BH24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ24" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10835,12 +10835,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM24" s="8" t="inlineStr">
+      <c r="BL24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM24" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10855,9 +10855,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP24" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -10882,9 +10882,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E25" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
@@ -10897,17 +10897,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J25" s="8" t="inlineStr">
+      <c r="H25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J25" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10922,7 +10922,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M25" s="8" t="inlineStr">
+      <c r="M25" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10932,12 +10932,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P25" s="8" t="inlineStr">
+      <c r="O25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P25" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10972,27 +10972,27 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AA25" s="8" t="inlineStr">
+      <c r="W25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA25" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11007,22 +11007,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG25" s="8" t="inlineStr">
+      <c r="AD25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG25" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11032,7 +11032,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI25" s="8" t="inlineStr">
+      <c r="AI25" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11057,7 +11057,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN25" s="8" t="inlineStr">
+      <c r="AN25" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11082,7 +11082,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS25" s="8" t="inlineStr">
+      <c r="AS25" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11092,12 +11092,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV25" s="8" t="inlineStr">
+      <c r="AU25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV25" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11107,22 +11107,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX25" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY25" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AZ25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BA25" s="8" t="inlineStr">
+      <c r="AX25" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY25" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AZ25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BA25" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11147,7 +11147,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BF25" s="8" t="inlineStr">
+      <c r="BF25" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11157,12 +11157,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BH25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI25" s="8" t="inlineStr">
+      <c r="BH25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI25" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11177,12 +11177,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM25" s="8" t="inlineStr">
+      <c r="BL25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM25" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11197,9 +11197,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP25" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -11218,7 +11218,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -11252,7 +11252,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>STM32WBA52KE</t>
+          <t>STM32WBA50KG</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -11267,14 +11267,14 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Table 31. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 25. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>STM32WBA55UE</t>
+          <t>STM32WBA52CE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -11289,271 +11289,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Table 31. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>STM32WBA50KG</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Table 25. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>STM32WBA52KG</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Table 31. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>STM32WBA54KG</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Table 31. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>STM32WBA52CG</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Table 31. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>STM32WBA55UG</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Table 31. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>STM32WBA55CE</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Table 31. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>STM32WBA52CE</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Table 31. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>STM32WBA54KE</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Table 31. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>STM32WBA54CE</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Table 31. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>STM32WBA55HG</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Table 31. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>STM32WBA54CG</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Table 31. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>STM32WBA55CG</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Table 31. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 31. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>

--- a/product_selector_out/STM32WBA5x.xlsx
+++ b/product_selector_out/STM32WBA5x.xlsx
@@ -61,12 +61,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
     <fill>
@@ -1350,7 +1350,7 @@
       </c>
       <c r="BP12" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wba52ce.pdf</t>
         </is>
       </c>
     </row>
@@ -1692,7 +1692,7 @@
       </c>
       <c r="BP13" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wba52ce.pdf</t>
         </is>
       </c>
     </row>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="BP15" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wba52ce.pdf</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="BP16" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wba52ce.pdf</t>
         </is>
       </c>
     </row>
@@ -3060,7 +3060,7 @@
       </c>
       <c r="BP17" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wba52ce.pdf</t>
         </is>
       </c>
     </row>
@@ -3402,7 +3402,7 @@
       </c>
       <c r="BP18" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wba52ce.pdf</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
       </c>
       <c r="BP19" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wba52ce.pdf</t>
         </is>
       </c>
     </row>
@@ -4428,7 +4428,7 @@
       </c>
       <c r="BP21" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wba52ce.pdf</t>
         </is>
       </c>
     </row>
@@ -4770,7 +4770,7 @@
       </c>
       <c r="BP22" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wba52ce.pdf</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="BP23" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wba52ce.pdf</t>
         </is>
       </c>
     </row>
@@ -5454,7 +5454,7 @@
       </c>
       <c r="BP24" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wba52ce.pdf</t>
         </is>
       </c>
     </row>
@@ -5796,7 +5796,7 @@
       </c>
       <c r="BP25" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wba52ce.pdf</t>
         </is>
       </c>
     </row>
@@ -6436,9 +6436,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
@@ -6451,17 +6451,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J12" s="7" t="inlineStr">
+      <c r="H12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6476,7 +6476,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M12" s="7" t="inlineStr">
+      <c r="M12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6486,17 +6486,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q12" s="7" t="inlineStr">
+      <c r="O12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6526,32 +6526,32 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AA12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AB12" s="7" t="inlineStr">
+      <c r="W12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AB12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6561,22 +6561,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG12" s="7" t="inlineStr">
+      <c r="AD12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6586,7 +6586,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI12" s="7" t="inlineStr">
+      <c r="AI12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6596,7 +6596,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK12" s="7" t="inlineStr">
+      <c r="AK12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6611,12 +6611,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AO12" s="7" t="inlineStr">
+      <c r="AN12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AO12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6636,7 +6636,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS12" s="7" t="inlineStr">
+      <c r="AS12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6646,37 +6646,37 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AX12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AZ12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BA12" s="7" t="inlineStr">
+      <c r="AU12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AX12" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY12" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="AZ12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BA12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6691,37 +6691,37 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BD12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ12" s="7" t="inlineStr">
+      <c r="BD12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6731,12 +6731,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM12" s="7" t="inlineStr">
+      <c r="BL12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6751,9 +6751,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP12" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -6778,9 +6778,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
@@ -6793,17 +6793,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J13" s="7" t="inlineStr">
+      <c r="H13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6818,7 +6818,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M13" s="7" t="inlineStr">
+      <c r="M13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6828,12 +6828,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P13" s="7" t="inlineStr">
+      <c r="O13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6868,27 +6868,27 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AA13" s="7" t="inlineStr">
+      <c r="W13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6903,22 +6903,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG13" s="7" t="inlineStr">
+      <c r="AD13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6928,7 +6928,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI13" s="7" t="inlineStr">
+      <c r="AI13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6953,7 +6953,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN13" s="7" t="inlineStr">
+      <c r="AN13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6978,7 +6978,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS13" s="7" t="inlineStr">
+      <c r="AS13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6988,12 +6988,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV13" s="7" t="inlineStr">
+      <c r="AU13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7003,22 +7003,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AZ13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BA13" s="7" t="inlineStr">
+      <c r="AX13" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY13" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="AZ13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BA13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7043,7 +7043,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BF13" s="7" t="inlineStr">
+      <c r="BF13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7053,17 +7053,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BH13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ13" s="7" t="inlineStr">
+      <c r="BH13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7073,12 +7073,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM13" s="7" t="inlineStr">
+      <c r="BL13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7093,9 +7093,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -7120,7 +7120,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E14" s="8" t="inlineStr">
+      <c r="E14" s="7" t="inlineStr">
         <is>
           <t>DATASHEET</t>
         </is>
@@ -7135,17 +7135,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J14" s="7" t="inlineStr">
+      <c r="H14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7160,7 +7160,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M14" s="7" t="inlineStr">
+      <c r="M14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7170,12 +7170,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P14" s="7" t="inlineStr">
+      <c r="O14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7210,27 +7210,27 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AA14" s="7" t="inlineStr">
+      <c r="W14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7245,22 +7245,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG14" s="7" t="inlineStr">
+      <c r="AD14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7270,7 +7270,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI14" s="7" t="inlineStr">
+      <c r="AI14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7295,7 +7295,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN14" s="7" t="inlineStr">
+      <c r="AN14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7320,7 +7320,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS14" s="7" t="inlineStr">
+      <c r="AS14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7330,17 +7330,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW14" s="7" t="inlineStr">
+      <c r="AU14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7350,17 +7350,17 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AY14" s="8" t="inlineStr">
+      <c r="AY14" s="7" t="inlineStr">
         <is>
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AZ14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BA14" s="7" t="inlineStr">
+      <c r="AZ14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BA14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7385,7 +7385,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BF14" s="7" t="inlineStr">
+      <c r="BF14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7395,17 +7395,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BH14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ14" s="7" t="inlineStr">
+      <c r="BH14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7415,12 +7415,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM14" s="7" t="inlineStr">
+      <c r="BL14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7462,9 +7462,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
@@ -7477,17 +7477,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J15" s="7" t="inlineStr">
+      <c r="H15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7502,7 +7502,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M15" s="7" t="inlineStr">
+      <c r="M15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7512,12 +7512,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P15" s="7" t="inlineStr">
+      <c r="O15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7552,32 +7552,32 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AA15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AB15" s="7" t="inlineStr">
+      <c r="W15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AB15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7587,22 +7587,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG15" s="7" t="inlineStr">
+      <c r="AD15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7612,7 +7612,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI15" s="7" t="inlineStr">
+      <c r="AI15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7622,7 +7622,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK15" s="7" t="inlineStr">
+      <c r="AK15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7637,12 +7637,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AO15" s="7" t="inlineStr">
+      <c r="AN15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AO15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7662,7 +7662,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS15" s="7" t="inlineStr">
+      <c r="AS15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7672,37 +7672,37 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AX15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AZ15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BA15" s="7" t="inlineStr">
+      <c r="AU15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AX15" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY15" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="AZ15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BA15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7717,37 +7717,37 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BD15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ15" s="7" t="inlineStr">
+      <c r="BD15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7757,12 +7757,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM15" s="7" t="inlineStr">
+      <c r="BL15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7777,9 +7777,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -7804,9 +7804,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
@@ -7819,17 +7819,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J16" s="7" t="inlineStr">
+      <c r="H16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7844,7 +7844,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M16" s="7" t="inlineStr">
+      <c r="M16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7854,12 +7854,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P16" s="7" t="inlineStr">
+      <c r="O16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7894,27 +7894,27 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AA16" s="7" t="inlineStr">
+      <c r="W16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7929,22 +7929,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG16" s="7" t="inlineStr">
+      <c r="AD16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7954,7 +7954,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI16" s="7" t="inlineStr">
+      <c r="AI16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7979,7 +7979,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN16" s="7" t="inlineStr">
+      <c r="AN16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8004,7 +8004,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS16" s="7" t="inlineStr">
+      <c r="AS16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8014,37 +8014,37 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AX16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AZ16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BA16" s="7" t="inlineStr">
+      <c r="AU16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AX16" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY16" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="AZ16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BA16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8069,7 +8069,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BF16" s="7" t="inlineStr">
+      <c r="BF16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8079,17 +8079,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BH16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ16" s="7" t="inlineStr">
+      <c r="BH16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8099,12 +8099,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM16" s="7" t="inlineStr">
+      <c r="BL16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8119,9 +8119,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -8146,9 +8146,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
@@ -8161,17 +8161,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J17" s="7" t="inlineStr">
+      <c r="H17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J17" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8186,7 +8186,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M17" s="7" t="inlineStr">
+      <c r="M17" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8196,17 +8196,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q17" s="7" t="inlineStr">
+      <c r="O17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q17" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8236,32 +8236,32 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AA17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AB17" s="7" t="inlineStr">
+      <c r="W17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AB17" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8271,22 +8271,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG17" s="7" t="inlineStr">
+      <c r="AD17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG17" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8296,7 +8296,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI17" s="7" t="inlineStr">
+      <c r="AI17" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8306,7 +8306,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK17" s="7" t="inlineStr">
+      <c r="AK17" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8321,17 +8321,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AO17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AP17" s="7" t="inlineStr">
+      <c r="AN17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AO17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AP17" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8346,7 +8346,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS17" s="7" t="inlineStr">
+      <c r="AS17" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8356,37 +8356,37 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AX17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AZ17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BA17" s="7" t="inlineStr">
+      <c r="AU17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AX17" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY17" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="AZ17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BA17" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8401,37 +8401,37 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BD17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ17" s="7" t="inlineStr">
+      <c r="BD17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ17" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8441,12 +8441,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM17" s="7" t="inlineStr">
+      <c r="BL17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM17" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8461,9 +8461,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -8488,9 +8488,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr">
@@ -8503,17 +8503,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J18" s="7" t="inlineStr">
+      <c r="H18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J18" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8528,7 +8528,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M18" s="7" t="inlineStr">
+      <c r="M18" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8538,12 +8538,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P18" s="7" t="inlineStr">
+      <c r="O18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P18" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8578,27 +8578,27 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AA18" s="7" t="inlineStr">
+      <c r="W18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA18" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8613,22 +8613,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG18" s="7" t="inlineStr">
+      <c r="AD18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG18" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8638,7 +8638,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI18" s="7" t="inlineStr">
+      <c r="AI18" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8663,7 +8663,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN18" s="7" t="inlineStr">
+      <c r="AN18" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8688,7 +8688,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS18" s="7" t="inlineStr">
+      <c r="AS18" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8698,12 +8698,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV18" s="7" t="inlineStr">
+      <c r="AU18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV18" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8713,22 +8713,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AZ18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BA18" s="7" t="inlineStr">
+      <c r="AX18" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY18" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="AZ18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BA18" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8753,7 +8753,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BF18" s="7" t="inlineStr">
+      <c r="BF18" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8763,17 +8763,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BH18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ18" s="7" t="inlineStr">
+      <c r="BH18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ18" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8783,12 +8783,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM18" s="7" t="inlineStr">
+      <c r="BL18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM18" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8803,9 +8803,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -8830,9 +8830,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
@@ -8845,17 +8845,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J19" s="7" t="inlineStr">
+      <c r="H19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J19" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8870,7 +8870,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M19" s="7" t="inlineStr">
+      <c r="M19" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8880,12 +8880,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P19" s="7" t="inlineStr">
+      <c r="O19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P19" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8920,27 +8920,27 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AA19" s="7" t="inlineStr">
+      <c r="W19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA19" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8955,22 +8955,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG19" s="7" t="inlineStr">
+      <c r="AD19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG19" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8980,7 +8980,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI19" s="7" t="inlineStr">
+      <c r="AI19" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9005,7 +9005,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN19" s="7" t="inlineStr">
+      <c r="AN19" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9030,7 +9030,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS19" s="7" t="inlineStr">
+      <c r="AS19" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9040,12 +9040,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV19" s="7" t="inlineStr">
+      <c r="AU19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV19" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9055,22 +9055,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AZ19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BA19" s="7" t="inlineStr">
+      <c r="AX19" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY19" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="AZ19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BA19" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9095,7 +9095,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BF19" s="7" t="inlineStr">
+      <c r="BF19" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9105,17 +9105,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BH19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ19" s="7" t="inlineStr">
+      <c r="BH19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ19" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9125,12 +9125,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM19" s="7" t="inlineStr">
+      <c r="BL19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM19" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9145,9 +9145,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -9172,7 +9172,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E20" s="8" t="inlineStr">
+      <c r="E20" s="7" t="inlineStr">
         <is>
           <t>DATASHEET</t>
         </is>
@@ -9187,17 +9187,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J20" s="7" t="inlineStr">
+      <c r="H20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J20" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9212,7 +9212,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M20" s="7" t="inlineStr">
+      <c r="M20" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9222,17 +9222,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q20" s="7" t="inlineStr">
+      <c r="O20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q20" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9262,32 +9262,32 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AA20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AB20" s="7" t="inlineStr">
+      <c r="W20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AB20" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9297,22 +9297,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG20" s="7" t="inlineStr">
+      <c r="AD20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG20" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9322,7 +9322,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI20" s="7" t="inlineStr">
+      <c r="AI20" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9332,7 +9332,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK20" s="7" t="inlineStr">
+      <c r="AK20" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9347,17 +9347,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AO20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AP20" s="7" t="inlineStr">
+      <c r="AN20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AO20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AP20" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9372,7 +9372,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS20" s="7" t="inlineStr">
+      <c r="AS20" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9382,17 +9382,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW20" s="7" t="inlineStr">
+      <c r="AU20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW20" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9402,17 +9402,17 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AY20" s="8" t="inlineStr">
+      <c r="AY20" s="7" t="inlineStr">
         <is>
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AZ20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BA20" s="7" t="inlineStr">
+      <c r="AZ20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BA20" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9427,37 +9427,37 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BD20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ20" s="7" t="inlineStr">
+      <c r="BD20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ20" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9467,12 +9467,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM20" s="7" t="inlineStr">
+      <c r="BL20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM20" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9514,9 +9514,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E21" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
@@ -9529,17 +9529,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J21" s="7" t="inlineStr">
+      <c r="H21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J21" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9554,7 +9554,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M21" s="7" t="inlineStr">
+      <c r="M21" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9564,12 +9564,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P21" s="7" t="inlineStr">
+      <c r="O21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P21" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9604,27 +9604,27 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AA21" s="7" t="inlineStr">
+      <c r="W21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA21" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9639,22 +9639,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG21" s="7" t="inlineStr">
+      <c r="AD21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG21" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9664,7 +9664,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI21" s="7" t="inlineStr">
+      <c r="AI21" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9689,7 +9689,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN21" s="7" t="inlineStr">
+      <c r="AN21" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9714,7 +9714,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS21" s="7" t="inlineStr">
+      <c r="AS21" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9724,37 +9724,37 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AX21" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY21" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AZ21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BA21" s="7" t="inlineStr">
+      <c r="AU21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AX21" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY21" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="AZ21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BA21" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9779,7 +9779,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BF21" s="7" t="inlineStr">
+      <c r="BF21" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9789,17 +9789,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BH21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ21" s="7" t="inlineStr">
+      <c r="BH21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ21" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9809,12 +9809,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM21" s="7" t="inlineStr">
+      <c r="BL21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM21" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9829,9 +9829,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP21" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -9856,9 +9856,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
@@ -9871,17 +9871,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J22" s="7" t="inlineStr">
+      <c r="H22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J22" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9896,7 +9896,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M22" s="7" t="inlineStr">
+      <c r="M22" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9906,12 +9906,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P22" s="7" t="inlineStr">
+      <c r="O22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P22" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9946,27 +9946,27 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AA22" s="7" t="inlineStr">
+      <c r="W22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA22" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9981,22 +9981,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG22" s="7" t="inlineStr">
+      <c r="AD22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG22" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10006,7 +10006,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI22" s="7" t="inlineStr">
+      <c r="AI22" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10031,7 +10031,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN22" s="7" t="inlineStr">
+      <c r="AN22" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10056,7 +10056,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS22" s="7" t="inlineStr">
+      <c r="AS22" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10066,37 +10066,37 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AX22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AZ22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BA22" s="7" t="inlineStr">
+      <c r="AU22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AX22" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY22" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="AZ22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BA22" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10121,7 +10121,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BF22" s="7" t="inlineStr">
+      <c r="BF22" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10131,17 +10131,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BH22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ22" s="7" t="inlineStr">
+      <c r="BH22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ22" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10151,12 +10151,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM22" s="7" t="inlineStr">
+      <c r="BL22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM22" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10171,9 +10171,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -10198,9 +10198,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
@@ -10213,17 +10213,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J23" s="7" t="inlineStr">
+      <c r="H23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J23" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10238,7 +10238,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M23" s="7" t="inlineStr">
+      <c r="M23" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10248,12 +10248,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P23" s="7" t="inlineStr">
+      <c r="O23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P23" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10288,27 +10288,27 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AA23" s="7" t="inlineStr">
+      <c r="W23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA23" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10323,22 +10323,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG23" s="7" t="inlineStr">
+      <c r="AD23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG23" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10348,7 +10348,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI23" s="7" t="inlineStr">
+      <c r="AI23" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10373,7 +10373,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN23" s="7" t="inlineStr">
+      <c r="AN23" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10398,7 +10398,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS23" s="7" t="inlineStr">
+      <c r="AS23" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10408,12 +10408,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV23" s="7" t="inlineStr">
+      <c r="AU23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV23" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10423,22 +10423,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AZ23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BA23" s="7" t="inlineStr">
+      <c r="AX23" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY23" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="AZ23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BA23" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10463,7 +10463,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BF23" s="7" t="inlineStr">
+      <c r="BF23" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10473,17 +10473,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BH23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ23" s="7" t="inlineStr">
+      <c r="BH23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ23" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10493,12 +10493,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM23" s="7" t="inlineStr">
+      <c r="BL23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM23" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10513,9 +10513,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -10540,9 +10540,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E24" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F24" s="6" t="inlineStr">
@@ -10555,17 +10555,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H24" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I24" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J24" s="7" t="inlineStr">
+      <c r="H24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J24" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10580,7 +10580,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M24" s="7" t="inlineStr">
+      <c r="M24" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10590,12 +10590,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O24" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P24" s="7" t="inlineStr">
+      <c r="O24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P24" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10630,27 +10630,27 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W24" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X24" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y24" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z24" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AA24" s="7" t="inlineStr">
+      <c r="W24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA24" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10665,22 +10665,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD24" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE24" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF24" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG24" s="7" t="inlineStr">
+      <c r="AD24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG24" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10690,7 +10690,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI24" s="7" t="inlineStr">
+      <c r="AI24" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10715,7 +10715,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN24" s="7" t="inlineStr">
+      <c r="AN24" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10740,7 +10740,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS24" s="7" t="inlineStr">
+      <c r="AS24" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10750,37 +10750,37 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU24" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV24" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW24" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AX24" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY24" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AZ24" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BA24" s="7" t="inlineStr">
+      <c r="AU24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AX24" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY24" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="AZ24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BA24" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10805,7 +10805,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BF24" s="7" t="inlineStr">
+      <c r="BF24" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10815,17 +10815,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BH24" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI24" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ24" s="7" t="inlineStr">
+      <c r="BH24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ24" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10835,12 +10835,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL24" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM24" s="7" t="inlineStr">
+      <c r="BL24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM24" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10855,9 +10855,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP24" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP24" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -10882,9 +10882,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E25" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
@@ -10897,17 +10897,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H25" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I25" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J25" s="7" t="inlineStr">
+      <c r="H25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J25" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10922,7 +10922,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M25" s="7" t="inlineStr">
+      <c r="M25" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10932,12 +10932,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O25" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P25" s="7" t="inlineStr">
+      <c r="O25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P25" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10972,27 +10972,27 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W25" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X25" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y25" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z25" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AA25" s="7" t="inlineStr">
+      <c r="W25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA25" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11007,22 +11007,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD25" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE25" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF25" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG25" s="7" t="inlineStr">
+      <c r="AD25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG25" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11032,7 +11032,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI25" s="7" t="inlineStr">
+      <c r="AI25" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11057,7 +11057,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN25" s="7" t="inlineStr">
+      <c r="AN25" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11082,7 +11082,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS25" s="7" t="inlineStr">
+      <c r="AS25" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11092,12 +11092,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU25" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV25" s="7" t="inlineStr">
+      <c r="AU25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV25" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11107,22 +11107,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX25" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY25" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AZ25" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BA25" s="7" t="inlineStr">
+      <c r="AX25" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY25" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="AZ25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BA25" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11147,7 +11147,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BF25" s="7" t="inlineStr">
+      <c r="BF25" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11157,12 +11157,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BH25" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI25" s="7" t="inlineStr">
+      <c r="BH25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI25" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11177,12 +11177,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL25" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM25" s="7" t="inlineStr">
+      <c r="BL25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM25" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11197,9 +11197,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP25" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP25" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -11218,7 +11218,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -11252,7 +11252,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>STM32WBA50KG</t>
+          <t>STM32WBA52KE</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -11267,27 +11267,291 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Table 25. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 31. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>STM32WBA55UE</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Table 31. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>STM32WBA50KG</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Table 25. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>STM32WBA52KG</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Table 31. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>STM32WBA54KG</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Table 31. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>STM32WBA52CG</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Table 31. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>STM32WBA55UG</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Table 31. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>STM32WBA55CE</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Table 31. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>STM32WBA52CE</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Supply Voltage (V) min</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Table 31. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>STM32WBA54KE</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Table 31. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>STM32WBA54CE</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Table 31. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>STM32WBA55HG</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Table 31. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>STM32WBA54CG</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Table 31. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>STM32WBA55CG</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
         <is>
           <t>Table 31. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>

--- a/product_selector_out/STM32WBA5x.xlsx
+++ b/product_selector_out/STM32WBA5x.xlsx
@@ -61,12 +61,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
@@ -1350,7 +1350,7 @@
       </c>
       <c r="BP12" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba52ce.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -1692,7 +1692,7 @@
       </c>
       <c r="BP13" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba52ce.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="BP15" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba52ce.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="BP16" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba52ce.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3060,7 +3060,7 @@
       </c>
       <c r="BP17" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba52ce.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3402,7 +3402,7 @@
       </c>
       <c r="BP18" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba52ce.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
       </c>
       <c r="BP19" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba52ce.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -4428,7 +4428,7 @@
       </c>
       <c r="BP21" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba52ce.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -4770,7 +4770,7 @@
       </c>
       <c r="BP22" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba52ce.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="BP23" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba52ce.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -5454,7 +5454,7 @@
       </c>
       <c r="BP24" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba52ce.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -5796,7 +5796,7 @@
       </c>
       <c r="BP25" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba52ce.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -6436,9 +6436,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
@@ -6451,17 +6451,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J12" s="8" t="inlineStr">
+      <c r="H12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6476,7 +6476,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M12" s="8" t="inlineStr">
+      <c r="M12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6486,17 +6486,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q12" s="8" t="inlineStr">
+      <c r="O12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6526,32 +6526,32 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AA12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AB12" s="8" t="inlineStr">
+      <c r="W12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AB12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6561,22 +6561,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG12" s="8" t="inlineStr">
+      <c r="AD12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6586,7 +6586,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI12" s="8" t="inlineStr">
+      <c r="AI12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6596,7 +6596,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK12" s="8" t="inlineStr">
+      <c r="AK12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6611,12 +6611,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AO12" s="8" t="inlineStr">
+      <c r="AN12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AO12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6636,7 +6636,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS12" s="8" t="inlineStr">
+      <c r="AS12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6646,37 +6646,37 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AX12" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY12" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AZ12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BA12" s="8" t="inlineStr">
+      <c r="AU12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AX12" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY12" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AZ12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BA12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6691,37 +6691,37 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BD12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ12" s="8" t="inlineStr">
+      <c r="BD12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6731,12 +6731,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM12" s="8" t="inlineStr">
+      <c r="BL12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6751,9 +6751,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -6778,9 +6778,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
@@ -6793,17 +6793,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J13" s="8" t="inlineStr">
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6818,7 +6818,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M13" s="8" t="inlineStr">
+      <c r="M13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6828,12 +6828,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P13" s="8" t="inlineStr">
+      <c r="O13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6868,27 +6868,27 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AA13" s="8" t="inlineStr">
+      <c r="W13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6903,22 +6903,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG13" s="8" t="inlineStr">
+      <c r="AD13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6928,7 +6928,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI13" s="8" t="inlineStr">
+      <c r="AI13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6953,7 +6953,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN13" s="8" t="inlineStr">
+      <c r="AN13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6978,7 +6978,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS13" s="8" t="inlineStr">
+      <c r="AS13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6988,12 +6988,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV13" s="8" t="inlineStr">
+      <c r="AU13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7003,22 +7003,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX13" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY13" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AZ13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BA13" s="8" t="inlineStr">
+      <c r="AX13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AZ13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BA13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7043,7 +7043,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BF13" s="8" t="inlineStr">
+      <c r="BF13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7053,17 +7053,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BH13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ13" s="8" t="inlineStr">
+      <c r="BH13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7073,12 +7073,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM13" s="8" t="inlineStr">
+      <c r="BL13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7093,9 +7093,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -7120,7 +7120,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
+      <c r="E14" s="8" t="inlineStr">
         <is>
           <t>DATASHEET</t>
         </is>
@@ -7135,17 +7135,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J14" s="8" t="inlineStr">
+      <c r="H14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7160,7 +7160,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M14" s="8" t="inlineStr">
+      <c r="M14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7170,12 +7170,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P14" s="8" t="inlineStr">
+      <c r="O14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7210,27 +7210,27 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AA14" s="8" t="inlineStr">
+      <c r="W14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7245,22 +7245,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG14" s="8" t="inlineStr">
+      <c r="AD14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7270,7 +7270,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI14" s="8" t="inlineStr">
+      <c r="AI14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7295,7 +7295,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN14" s="8" t="inlineStr">
+      <c r="AN14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7320,7 +7320,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS14" s="8" t="inlineStr">
+      <c r="AS14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7330,17 +7330,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW14" s="8" t="inlineStr">
+      <c r="AU14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7350,17 +7350,17 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AY14" s="7" t="inlineStr">
+      <c r="AY14" s="8" t="inlineStr">
         <is>
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AZ14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BA14" s="8" t="inlineStr">
+      <c r="AZ14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BA14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7385,7 +7385,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BF14" s="8" t="inlineStr">
+      <c r="BF14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7395,17 +7395,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BH14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ14" s="8" t="inlineStr">
+      <c r="BH14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7415,12 +7415,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM14" s="8" t="inlineStr">
+      <c r="BL14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7462,9 +7462,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E15" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
@@ -7477,17 +7477,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J15" s="8" t="inlineStr">
+      <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7502,7 +7502,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M15" s="8" t="inlineStr">
+      <c r="M15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7512,12 +7512,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P15" s="8" t="inlineStr">
+      <c r="O15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7552,32 +7552,32 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AA15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AB15" s="8" t="inlineStr">
+      <c r="W15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AB15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7587,22 +7587,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG15" s="8" t="inlineStr">
+      <c r="AD15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7612,7 +7612,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI15" s="8" t="inlineStr">
+      <c r="AI15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7622,7 +7622,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK15" s="8" t="inlineStr">
+      <c r="AK15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7637,12 +7637,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AO15" s="8" t="inlineStr">
+      <c r="AN15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AO15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7662,7 +7662,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS15" s="8" t="inlineStr">
+      <c r="AS15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7672,37 +7672,37 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AX15" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY15" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AZ15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BA15" s="8" t="inlineStr">
+      <c r="AU15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AX15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AZ15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BA15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7717,37 +7717,37 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BD15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ15" s="8" t="inlineStr">
+      <c r="BD15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7757,12 +7757,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM15" s="8" t="inlineStr">
+      <c r="BL15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7777,9 +7777,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -7804,9 +7804,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
@@ -7819,17 +7819,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J16" s="8" t="inlineStr">
+      <c r="H16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7844,7 +7844,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M16" s="8" t="inlineStr">
+      <c r="M16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7854,12 +7854,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P16" s="8" t="inlineStr">
+      <c r="O16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7894,27 +7894,27 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AA16" s="8" t="inlineStr">
+      <c r="W16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7929,22 +7929,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG16" s="8" t="inlineStr">
+      <c r="AD16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7954,7 +7954,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI16" s="8" t="inlineStr">
+      <c r="AI16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7979,7 +7979,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN16" s="8" t="inlineStr">
+      <c r="AN16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8004,7 +8004,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS16" s="8" t="inlineStr">
+      <c r="AS16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8014,37 +8014,37 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AX16" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY16" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AZ16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BA16" s="8" t="inlineStr">
+      <c r="AU16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AX16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AZ16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BA16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8069,7 +8069,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BF16" s="8" t="inlineStr">
+      <c r="BF16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8079,17 +8079,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BH16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ16" s="8" t="inlineStr">
+      <c r="BH16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8099,12 +8099,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM16" s="8" t="inlineStr">
+      <c r="BL16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8119,9 +8119,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -8146,9 +8146,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E17" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
@@ -8161,17 +8161,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J17" s="8" t="inlineStr">
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8186,7 +8186,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M17" s="8" t="inlineStr">
+      <c r="M17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8196,17 +8196,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q17" s="8" t="inlineStr">
+      <c r="O17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8236,32 +8236,32 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AA17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AB17" s="8" t="inlineStr">
+      <c r="W17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AB17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8271,22 +8271,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG17" s="8" t="inlineStr">
+      <c r="AD17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8296,7 +8296,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI17" s="8" t="inlineStr">
+      <c r="AI17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8306,7 +8306,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK17" s="8" t="inlineStr">
+      <c r="AK17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8321,17 +8321,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AO17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AP17" s="8" t="inlineStr">
+      <c r="AN17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AO17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AP17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8346,7 +8346,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS17" s="8" t="inlineStr">
+      <c r="AS17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8356,37 +8356,37 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AX17" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY17" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AZ17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BA17" s="8" t="inlineStr">
+      <c r="AU17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AX17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AZ17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BA17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8401,37 +8401,37 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BD17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ17" s="8" t="inlineStr">
+      <c r="BD17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8441,12 +8441,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM17" s="8" t="inlineStr">
+      <c r="BL17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8461,9 +8461,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -8488,9 +8488,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E18" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr">
@@ -8503,17 +8503,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J18" s="8" t="inlineStr">
+      <c r="H18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8528,7 +8528,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M18" s="8" t="inlineStr">
+      <c r="M18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8538,12 +8538,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P18" s="8" t="inlineStr">
+      <c r="O18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8578,27 +8578,27 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AA18" s="8" t="inlineStr">
+      <c r="W18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8613,22 +8613,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG18" s="8" t="inlineStr">
+      <c r="AD18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8638,7 +8638,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI18" s="8" t="inlineStr">
+      <c r="AI18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8663,7 +8663,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN18" s="8" t="inlineStr">
+      <c r="AN18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8688,7 +8688,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS18" s="8" t="inlineStr">
+      <c r="AS18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8698,12 +8698,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV18" s="8" t="inlineStr">
+      <c r="AU18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8713,22 +8713,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX18" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY18" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AZ18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BA18" s="8" t="inlineStr">
+      <c r="AX18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AZ18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BA18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8753,7 +8753,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BF18" s="8" t="inlineStr">
+      <c r="BF18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8763,17 +8763,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BH18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ18" s="8" t="inlineStr">
+      <c r="BH18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8783,12 +8783,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM18" s="8" t="inlineStr">
+      <c r="BL18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8803,9 +8803,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -8830,9 +8830,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E19" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
@@ -8845,17 +8845,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J19" s="8" t="inlineStr">
+      <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8870,7 +8870,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M19" s="8" t="inlineStr">
+      <c r="M19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8880,12 +8880,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P19" s="8" t="inlineStr">
+      <c r="O19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8920,27 +8920,27 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AA19" s="8" t="inlineStr">
+      <c r="W19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8955,22 +8955,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG19" s="8" t="inlineStr">
+      <c r="AD19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8980,7 +8980,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI19" s="8" t="inlineStr">
+      <c r="AI19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9005,7 +9005,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN19" s="8" t="inlineStr">
+      <c r="AN19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9030,7 +9030,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS19" s="8" t="inlineStr">
+      <c r="AS19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9040,12 +9040,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV19" s="8" t="inlineStr">
+      <c r="AU19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9055,22 +9055,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX19" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY19" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AZ19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BA19" s="8" t="inlineStr">
+      <c r="AX19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AZ19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BA19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9095,7 +9095,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BF19" s="8" t="inlineStr">
+      <c r="BF19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9105,17 +9105,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BH19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ19" s="8" t="inlineStr">
+      <c r="BH19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9125,12 +9125,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM19" s="8" t="inlineStr">
+      <c r="BL19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9145,9 +9145,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -9172,7 +9172,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E20" s="7" t="inlineStr">
+      <c r="E20" s="8" t="inlineStr">
         <is>
           <t>DATASHEET</t>
         </is>
@@ -9187,17 +9187,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J20" s="8" t="inlineStr">
+      <c r="H20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J20" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9212,7 +9212,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M20" s="8" t="inlineStr">
+      <c r="M20" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9222,17 +9222,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q20" s="8" t="inlineStr">
+      <c r="O20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q20" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9262,32 +9262,32 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AA20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AB20" s="8" t="inlineStr">
+      <c r="W20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AB20" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9297,22 +9297,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG20" s="8" t="inlineStr">
+      <c r="AD20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG20" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9322,7 +9322,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI20" s="8" t="inlineStr">
+      <c r="AI20" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9332,7 +9332,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK20" s="8" t="inlineStr">
+      <c r="AK20" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9347,17 +9347,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AO20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AP20" s="8" t="inlineStr">
+      <c r="AN20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AO20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AP20" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9372,7 +9372,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS20" s="8" t="inlineStr">
+      <c r="AS20" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9382,17 +9382,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW20" s="8" t="inlineStr">
+      <c r="AU20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW20" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9402,17 +9402,17 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AY20" s="7" t="inlineStr">
+      <c r="AY20" s="8" t="inlineStr">
         <is>
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AZ20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BA20" s="8" t="inlineStr">
+      <c r="AZ20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BA20" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9427,37 +9427,37 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BD20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ20" s="8" t="inlineStr">
+      <c r="BD20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ20" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9467,12 +9467,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM20" s="8" t="inlineStr">
+      <c r="BL20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM20" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9514,9 +9514,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E21" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
@@ -9529,17 +9529,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J21" s="8" t="inlineStr">
+      <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J21" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9554,7 +9554,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M21" s="8" t="inlineStr">
+      <c r="M21" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9564,12 +9564,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P21" s="8" t="inlineStr">
+      <c r="O21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P21" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9604,27 +9604,27 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AA21" s="8" t="inlineStr">
+      <c r="W21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA21" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9639,22 +9639,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG21" s="8" t="inlineStr">
+      <c r="AD21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG21" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9664,7 +9664,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI21" s="8" t="inlineStr">
+      <c r="AI21" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9689,7 +9689,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN21" s="8" t="inlineStr">
+      <c r="AN21" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9714,7 +9714,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS21" s="8" t="inlineStr">
+      <c r="AS21" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9724,37 +9724,37 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AX21" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY21" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AZ21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BA21" s="8" t="inlineStr">
+      <c r="AU21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AX21" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY21" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AZ21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BA21" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9779,7 +9779,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BF21" s="8" t="inlineStr">
+      <c r="BF21" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9789,17 +9789,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BH21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ21" s="8" t="inlineStr">
+      <c r="BH21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ21" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9809,12 +9809,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM21" s="8" t="inlineStr">
+      <c r="BL21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM21" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9829,9 +9829,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP21" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -9856,9 +9856,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E22" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
@@ -9871,17 +9871,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J22" s="8" t="inlineStr">
+      <c r="H22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J22" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9896,7 +9896,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M22" s="8" t="inlineStr">
+      <c r="M22" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9906,12 +9906,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P22" s="8" t="inlineStr">
+      <c r="O22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P22" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9946,27 +9946,27 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AA22" s="8" t="inlineStr">
+      <c r="W22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA22" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9981,22 +9981,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG22" s="8" t="inlineStr">
+      <c r="AD22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG22" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10006,7 +10006,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI22" s="8" t="inlineStr">
+      <c r="AI22" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10031,7 +10031,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN22" s="8" t="inlineStr">
+      <c r="AN22" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10056,7 +10056,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS22" s="8" t="inlineStr">
+      <c r="AS22" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10066,37 +10066,37 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AX22" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY22" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AZ22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BA22" s="8" t="inlineStr">
+      <c r="AU22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AX22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AZ22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BA22" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10121,7 +10121,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BF22" s="8" t="inlineStr">
+      <c r="BF22" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10131,17 +10131,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BH22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ22" s="8" t="inlineStr">
+      <c r="BH22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ22" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10151,12 +10151,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM22" s="8" t="inlineStr">
+      <c r="BL22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM22" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10171,9 +10171,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -10198,9 +10198,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E23" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
@@ -10213,17 +10213,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J23" s="8" t="inlineStr">
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J23" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10238,7 +10238,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M23" s="8" t="inlineStr">
+      <c r="M23" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10248,12 +10248,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P23" s="8" t="inlineStr">
+      <c r="O23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P23" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10288,27 +10288,27 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AA23" s="8" t="inlineStr">
+      <c r="W23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA23" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10323,22 +10323,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG23" s="8" t="inlineStr">
+      <c r="AD23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG23" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10348,7 +10348,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI23" s="8" t="inlineStr">
+      <c r="AI23" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10373,7 +10373,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN23" s="8" t="inlineStr">
+      <c r="AN23" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10398,7 +10398,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS23" s="8" t="inlineStr">
+      <c r="AS23" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10408,12 +10408,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV23" s="8" t="inlineStr">
+      <c r="AU23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV23" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10423,22 +10423,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX23" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY23" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AZ23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BA23" s="8" t="inlineStr">
+      <c r="AX23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AZ23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BA23" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10463,7 +10463,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BF23" s="8" t="inlineStr">
+      <c r="BF23" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10473,17 +10473,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BH23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ23" s="8" t="inlineStr">
+      <c r="BH23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ23" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10493,12 +10493,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM23" s="8" t="inlineStr">
+      <c r="BL23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM23" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10513,9 +10513,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -10540,9 +10540,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E24" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F24" s="6" t="inlineStr">
@@ -10555,17 +10555,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J24" s="8" t="inlineStr">
+      <c r="H24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J24" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10580,7 +10580,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M24" s="8" t="inlineStr">
+      <c r="M24" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10590,12 +10590,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P24" s="8" t="inlineStr">
+      <c r="O24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P24" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10630,27 +10630,27 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AA24" s="8" t="inlineStr">
+      <c r="W24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA24" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10665,22 +10665,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG24" s="8" t="inlineStr">
+      <c r="AD24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG24" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10690,7 +10690,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI24" s="8" t="inlineStr">
+      <c r="AI24" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10715,7 +10715,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN24" s="8" t="inlineStr">
+      <c r="AN24" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10740,7 +10740,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS24" s="8" t="inlineStr">
+      <c r="AS24" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10750,37 +10750,37 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AX24" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY24" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AZ24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BA24" s="8" t="inlineStr">
+      <c r="AU24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AX24" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY24" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AZ24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BA24" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10805,7 +10805,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BF24" s="8" t="inlineStr">
+      <c r="BF24" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10815,17 +10815,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BH24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ24" s="8" t="inlineStr">
+      <c r="BH24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ24" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10835,12 +10835,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM24" s="8" t="inlineStr">
+      <c r="BL24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM24" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10855,9 +10855,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP24" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -10882,9 +10882,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E25" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
@@ -10897,17 +10897,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J25" s="8" t="inlineStr">
+      <c r="H25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J25" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10922,7 +10922,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M25" s="8" t="inlineStr">
+      <c r="M25" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10932,12 +10932,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P25" s="8" t="inlineStr">
+      <c r="O25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P25" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10972,27 +10972,27 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AA25" s="8" t="inlineStr">
+      <c r="W25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA25" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11007,22 +11007,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG25" s="8" t="inlineStr">
+      <c r="AD25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG25" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11032,7 +11032,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI25" s="8" t="inlineStr">
+      <c r="AI25" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11057,7 +11057,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN25" s="8" t="inlineStr">
+      <c r="AN25" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11082,7 +11082,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS25" s="8" t="inlineStr">
+      <c r="AS25" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11092,12 +11092,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV25" s="8" t="inlineStr">
+      <c r="AU25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV25" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11107,22 +11107,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX25" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY25" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AZ25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BA25" s="8" t="inlineStr">
+      <c r="AX25" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY25" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AZ25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BA25" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11147,7 +11147,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BF25" s="8" t="inlineStr">
+      <c r="BF25" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11157,12 +11157,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BH25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI25" s="8" t="inlineStr">
+      <c r="BH25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI25" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11177,12 +11177,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM25" s="8" t="inlineStr">
+      <c r="BL25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM25" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11197,9 +11197,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP25" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -11218,7 +11218,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -11252,7 +11252,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>STM32WBA52KE</t>
+          <t>STM32WBA50KG</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -11267,14 +11267,14 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Table 31. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 25. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>STM32WBA55UE</t>
+          <t>STM32WBA52CE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -11288,270 +11288,6 @@
         </is>
       </c>
       <c r="D3" t="inlineStr">
-        <is>
-          <t>Table 31. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>STM32WBA50KG</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Table 25. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>STM32WBA52KG</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Table 31. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>STM32WBA54KG</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Table 31. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>STM32WBA52CG</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Table 31. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>STM32WBA55UG</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Table 31. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>STM32WBA55CE</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Table 31. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>STM32WBA52CE</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Table 31. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>STM32WBA54KE</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Table 31. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>STM32WBA54CE</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Table 31. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>STM32WBA55HG</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Table 31. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>STM32WBA54CG</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Table 31. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>STM32WBA55CG</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
         <is>
           <t>Table 31. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>

--- a/product_selector_out/STM32WBA5x.xlsx
+++ b/product_selector_out/STM32WBA5x.xlsx
@@ -500,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP25"/>
+  <dimension ref="A1:BQ25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14.421875" customWidth="1" min="1" max="1"/>
@@ -570,7 +570,8 @@
     <col width="21.984375" customWidth="1" min="65" max="65"/>
     <col width="18" customWidth="1" min="66" max="66"/>
     <col width="18" customWidth="1" min="67" max="67"/>
-    <col width="52" customWidth="1" min="68" max="68"/>
+    <col width="18" customWidth="1" min="68" max="68"/>
+    <col width="52" customWidth="1" min="69" max="69"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -913,6 +914,11 @@
         </is>
       </c>
       <c r="BP10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BQ10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -1011,6 +1017,7 @@
       <c r="BN11" s="2" t="n"/>
       <c r="BO11" s="2" t="n"/>
       <c r="BP11" s="2" t="n"/>
+      <c r="BQ11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1353,6 +1360,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ12" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -1695,6 +1707,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ13" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -2034,6 +2051,11 @@
       </c>
       <c r="BP14" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BQ14" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32wba50kg.pdf</t>
         </is>
       </c>
@@ -2379,6 +2401,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ15" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
@@ -2721,6 +2748,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ16" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -3063,6 +3095,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ17" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
@@ -3405,6 +3442,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ18" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
@@ -3747,6 +3789,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ19" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
@@ -4086,6 +4133,11 @@
       </c>
       <c r="BP20" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BQ20" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32wba52ce.pdf</t>
         </is>
       </c>
@@ -4431,6 +4483,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ21" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
@@ -4773,6 +4830,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ22" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
@@ -5115,6 +5177,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ23" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
@@ -5457,6 +5524,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ24" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
@@ -5799,9 +5871,14 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ25" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="67">
+  <mergeCells count="68">
     <mergeCell ref="P10:P11"/>
     <mergeCell ref="AS10:AS11"/>
     <mergeCell ref="AD10:AD11"/>
@@ -5824,14 +5901,13 @@
     <mergeCell ref="Q10:Q11"/>
     <mergeCell ref="AR10:AR11"/>
     <mergeCell ref="AT10:AT11"/>
-    <mergeCell ref="A9:BP9"/>
+    <mergeCell ref="A1:BQ8"/>
     <mergeCell ref="S10:S11"/>
-    <mergeCell ref="A1:BP8"/>
     <mergeCell ref="AV10:AV11"/>
     <mergeCell ref="BB10:BB11"/>
     <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="BD10:BD11"/>
-    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="Y10:Z10"/>
     <mergeCell ref="AC10:AC11"/>
     <mergeCell ref="B10:B11"/>
@@ -5849,6 +5925,7 @@
     <mergeCell ref="BP10:BP11"/>
     <mergeCell ref="BK10:BK11"/>
     <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A9:BQ9"/>
     <mergeCell ref="I10:I11"/>
     <mergeCell ref="AL10:AL11"/>
     <mergeCell ref="K10:K11"/>
@@ -5861,6 +5938,7 @@
     <mergeCell ref="AX10:AX11"/>
     <mergeCell ref="AZ10:AZ11"/>
     <mergeCell ref="BF10:BF11"/>
+    <mergeCell ref="BQ10:BQ11"/>
     <mergeCell ref="R10:R11"/>
     <mergeCell ref="U10:V10"/>
     <mergeCell ref="BO10:BO11"/>
@@ -5897,7 +5975,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP25"/>
+  <dimension ref="A1:BQ25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5968,6 +6046,7 @@
     <col width="16" customWidth="1" min="66" max="66"/>
     <col width="16" customWidth="1" min="67" max="67"/>
     <col width="16" customWidth="1" min="68" max="68"/>
+    <col width="16" customWidth="1" min="69" max="69"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6316,6 +6395,11 @@
         </is>
       </c>
       <c r="BP10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BQ10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -6414,6 +6498,7 @@
       <c r="BN11" s="2" t="n"/>
       <c r="BO11" s="2" t="n"/>
       <c r="BP11" s="2" t="n"/>
+      <c r="BQ11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -6756,6 +6841,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -7098,6 +7188,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -7435,7 +7530,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP14" s="6" t="inlineStr">
+      <c r="BP14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BQ14" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -7782,6 +7882,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -8124,6 +8229,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
@@ -8466,6 +8576,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -8808,6 +8923,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -9150,6 +9270,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
@@ -9487,7 +9612,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP20" s="6" t="inlineStr">
+      <c r="BP20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BQ20" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -9834,6 +9964,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -10176,6 +10311,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
@@ -10518,6 +10658,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
@@ -10860,6 +11005,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
@@ -11202,11 +11352,16 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:BP8"/>
-    <mergeCell ref="A9:BP9"/>
+    <mergeCell ref="A1:BQ8"/>
+    <mergeCell ref="A9:BQ9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
